--- a/dataset/construct/dataset_splits/data_size/20_percent/merged/fold4.xlsx
+++ b/dataset/construct/dataset_splits/data_size/20_percent/merged/fold4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN37"/>
+  <dimension ref="A1:AK37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1314</v>
+        <v>2513</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,94 +625,94 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>79.1469129464852</v>
+        <v>84.37595016731311</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>24.6755002704164</v>
       </c>
       <c r="E2" t="n">
-        <v>31.833910034602</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>50</v>
+        <v>392.4</v>
       </c>
       <c r="I2" t="n">
-        <v>1150</v>
+        <v>407.3</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>215.7</v>
       </c>
       <c r="K2" t="n">
-        <v>120.5</v>
+        <v>1015.4</v>
       </c>
       <c r="L2" t="n">
-        <v>175.9</v>
+        <v>52.4</v>
       </c>
       <c r="M2" t="n">
-        <v>229.1</v>
+        <v>28.3</v>
       </c>
       <c r="N2" t="n">
-        <v>525.5</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>35.9</v>
+        <v>80.7</v>
       </c>
       <c r="P2" t="n">
-        <v>28.7</v>
+        <v>24.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>27.5</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>92.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>24.1</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>25.53</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>25.305576776165</v>
       </c>
       <c r="X2" t="n">
-        <v>23</v>
+        <v>25.0017500819378</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.270676691729323</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>24.2869875222816</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>23.3675988578761</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -739,22 +724,15 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>106</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
+        <v>246</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2008</v>
+        <v>2583</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -762,79 +740,79 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>86.27327024235051</v>
+        <v>85.0467322926965</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>26.2975778546712</v>
       </c>
       <c r="E3" t="n">
-        <v>26.4462809917355</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>50</v>
+        <v>664</v>
       </c>
       <c r="I3" t="n">
-        <v>34000</v>
+        <v>401</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>318</v>
       </c>
       <c r="K3" t="n">
-        <v>245.9</v>
+        <v>1383</v>
       </c>
       <c r="L3" t="n">
-        <v>53.9</v>
+        <v>37</v>
       </c>
       <c r="M3" t="n">
-        <v>59.7</v>
+        <v>8</v>
       </c>
       <c r="N3" t="n">
-        <v>359.5</v>
+        <v>95</v>
       </c>
       <c r="O3" t="n">
-        <v>46.7</v>
+        <v>140</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>16.1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>62.8</v>
+        <v>7</v>
       </c>
       <c r="S3" t="n">
-        <v>6.1</v>
+        <v>7</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>24.65</v>
       </c>
       <c r="V3" t="n">
-        <v>6.1</v>
+        <v>0.22</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>24.8281130634072</v>
       </c>
       <c r="X3" t="n">
-        <v>23.75</v>
+        <v>24.3439993862133</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.207547169811321</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.6822001527884</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.3621512301397</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -852,7 +830,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
         <v>0</v>
@@ -861,22 +839,15 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>88</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+        <v>154</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>555</v>
+        <v>2886</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -884,79 +855,79 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>82.8866092478516</v>
+        <v>87.4232017960808</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>31.3145661157024</v>
       </c>
       <c r="E4" t="n">
-        <v>26.4235698242832</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>36</v>
+        <v>569</v>
       </c>
       <c r="I4" t="n">
-        <v>1160</v>
+        <v>741</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>592</v>
       </c>
       <c r="K4" t="n">
-        <v>236</v>
+        <v>1902</v>
       </c>
       <c r="L4" t="n">
-        <v>300</v>
+        <v>261</v>
       </c>
       <c r="M4" t="n">
-        <v>165</v>
+        <v>29</v>
       </c>
       <c r="N4" t="n">
-        <v>701</v>
+        <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>16</v>
+        <v>390</v>
       </c>
       <c r="P4" t="n">
-        <v>10</v>
+        <v>93</v>
       </c>
       <c r="Q4" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>26</v>
+        <v>24.35</v>
       </c>
       <c r="V4" t="n">
-        <v>26</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>23.9686783804431</v>
       </c>
       <c r="X4" t="n">
-        <v>23.3</v>
+        <v>23.3675988578761</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.158102766798419</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>23.2365673542144</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>23.1211849536588</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -965,13 +936,13 @@
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -983,24 +954,15 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>170</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>550</v>
+        <v>700</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1008,88 +970,88 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>82.4873716632443</v>
+        <v>86.8191345349456</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>25.6055363321799</v>
       </c>
       <c r="E5" t="n">
-        <v>24.4897959183673</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>50</v>
+        <v>420</v>
       </c>
       <c r="I5" t="n">
-        <v>18300</v>
+        <v>285</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>308</v>
       </c>
       <c r="K5" t="n">
-        <v>694</v>
+        <v>1013</v>
       </c>
       <c r="L5" t="n">
-        <v>856</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1059</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2609</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>23.8</v>
       </c>
       <c r="V5" t="n">
-        <v>11</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>23.554876496053</v>
       </c>
       <c r="X5" t="n">
-        <v>25.3</v>
+        <v>23.4220054480732</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.255172413793103</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>26.4196587726</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>25.6028939368547</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1098,31 +1060,24 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>126</v>
-      </c>
-      <c r="AN5" t="inlineStr"/>
+        <v>190</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>601</v>
+        <v>500</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1130,123 +1085,112 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>88.0775420184044</v>
+        <v>71.47246748802191</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>24.1671624033313</v>
       </c>
       <c r="E6" t="n">
-        <v>22.9004724889498</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>40</v>
+        <v>168.7</v>
       </c>
       <c r="I6" t="n">
-        <v>8530</v>
+        <v>83</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>128.9</v>
       </c>
       <c r="K6" t="n">
-        <v>764</v>
+        <v>380.6</v>
       </c>
       <c r="L6" t="n">
-        <v>756</v>
+        <v>23.7</v>
       </c>
       <c r="M6" t="n">
-        <v>552</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2072</v>
+        <v>12.6</v>
       </c>
       <c r="O6" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>8</v>
+      </c>
+      <c r="S6" t="n">
+        <v>8</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="W6" t="n">
+        <v>25.3692386045327</v>
+      </c>
+      <c r="X6" t="n">
+        <v>24.7150115381059</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>93</v>
       </c>
-      <c r="P6" t="n">
-        <v>75</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>78</v>
-      </c>
-      <c r="R6" t="n">
-        <v>246</v>
-      </c>
-      <c r="S6" t="n">
-        <v>34</v>
-      </c>
-      <c r="T6" t="n">
-        <v>10</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>44</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2</v>
-      </c>
-      <c r="X6" t="n">
-        <v>23.15</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.278810408921933</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>23.8731856378915</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>22.9831467948561</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>116</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>128</v>
-      </c>
+      <c r="AK6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>340</v>
+        <v>656</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1254,41 +1198,43 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>79.8069135485588</v>
+        <v>86.7305080868</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>21.3406795224977</v>
       </c>
       <c r="E7" t="n">
-        <v>27.6816608996539</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>60</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
+        <v>286.8</v>
+      </c>
+      <c r="I7" t="n">
+        <v>357.2</v>
+      </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>166.4</v>
       </c>
       <c r="K7" t="n">
-        <v>520</v>
+        <v>810.4</v>
       </c>
       <c r="L7" t="n">
-        <v>304</v>
+        <v>12.2</v>
       </c>
       <c r="M7" t="n">
-        <v>172</v>
+        <v>28.3</v>
       </c>
       <c r="N7" t="n">
-        <v>996</v>
+        <v>5.7</v>
       </c>
       <c r="O7" t="n">
-        <v>18</v>
+        <v>46.2</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1297,37 +1243,37 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>23.65</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>23.7458619811561</v>
       </c>
       <c r="X7" t="n">
-        <v>25.75</v>
+        <v>23.5115010765807</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.217993079584775</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>25.528393175452</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>25.055148236001</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1339,10 +1285,10 @@
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
@@ -1351,24 +1297,13 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>91</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>180</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="AK7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2607</v>
+        <v>1228</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1376,43 +1311,43 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>81.77774745227769</v>
+        <v>85.5069068623723</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>32.4556777151202</v>
       </c>
       <c r="E8" t="n">
-        <v>28.1969212010364</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>56</v>
+        <v>39.8</v>
       </c>
       <c r="I8" t="n">
-        <v>536</v>
+        <v>30.3</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>26.9</v>
       </c>
       <c r="K8" t="n">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="L8" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1421,34 +1356,34 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>21.55</v>
       </c>
       <c r="V8" t="n">
-        <v>8</v>
+        <v>0.34</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>22.5362872421696</v>
       </c>
       <c r="X8" t="n">
-        <v>23.5</v>
+        <v>21.3554558707986</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.272058823529412</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>23.5867074102368</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>22.8860247016979</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1469,30 +1404,21 @@
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>82</v>
-      </c>
-      <c r="AN8" t="n">
         <v>210</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1025</v>
+        <v>1019</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1500,85 +1426,85 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>85.2467825500038</v>
+        <v>84.97033370725281</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>30.1109905115367</v>
       </c>
       <c r="E9" t="n">
-        <v>30.3460743801652</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>42</v>
+        <v>156</v>
       </c>
       <c r="I9" t="n">
-        <v>3370</v>
+        <v>152</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>253</v>
       </c>
       <c r="K9" t="n">
-        <v>242.8</v>
+        <v>561</v>
       </c>
       <c r="L9" t="n">
-        <v>371.3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>285.3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>899.4</v>
+        <v>98</v>
       </c>
       <c r="O9" t="n">
-        <v>72.3</v>
+        <v>98</v>
       </c>
       <c r="P9" t="n">
-        <v>106.7</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>85.3</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>264.3</v>
+        <v>96</v>
       </c>
       <c r="S9" t="n">
-        <v>22.6</v>
+        <v>96</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>53.2</v>
+        <v>24.3</v>
       </c>
       <c r="V9" t="n">
-        <v>75.8</v>
+        <v>0.23</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>24.1914947797301</v>
       </c>
       <c r="X9" t="n">
-        <v>26.9</v>
+        <v>23.6114412754479</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.16382252559727</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>27.1836007130125</v>
+        <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>26.8217134966894</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1590,31 +1516,24 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>86</v>
-      </c>
-      <c r="AN9" t="inlineStr"/>
+        <v>180</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>914</v>
+        <v>1427</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1622,79 +1541,79 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>84.0671732958146</v>
+        <v>86.99098473901689</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>25.2080856123662</v>
       </c>
       <c r="E10" t="n">
-        <v>25.7629805786761</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>60</v>
+        <v>319.5</v>
       </c>
       <c r="I10" t="n">
-        <v>1400</v>
+        <v>203</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>264.3</v>
       </c>
       <c r="K10" t="n">
-        <v>855</v>
+        <v>786.8</v>
       </c>
       <c r="L10" t="n">
-        <v>534</v>
+        <v>36.6</v>
       </c>
       <c r="M10" t="n">
-        <v>428</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1817</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>50</v>
+        <v>36.6</v>
       </c>
       <c r="P10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>93</v>
+        <v>22.35</v>
       </c>
       <c r="V10" t="n">
-        <v>93</v>
+        <v>0.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>23.0137509549274</v>
       </c>
       <c r="X10" t="n">
-        <v>29</v>
+        <v>22.1512191514658</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.220858895705522</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="n">
-        <v>29.921059332824</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>29.2679951700071</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1715,28 +1634,21 @@
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AK10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
         <v>154</v>
       </c>
-      <c r="AN10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2106</v>
+        <v>1314</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1744,77 +1656,79 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>87.3656652597156</v>
+        <v>79.1469129464852</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>31.833910034602</v>
       </c>
       <c r="E11" t="n">
-        <v>29.0858725761772</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>45</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
+        <v>120.5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>175.9</v>
+      </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>229.1</v>
       </c>
       <c r="K11" t="n">
-        <v>327.7</v>
+        <v>525.5</v>
       </c>
       <c r="L11" t="n">
-        <v>332.3</v>
+        <v>35.9</v>
       </c>
       <c r="M11" t="n">
-        <v>320.1</v>
+        <v>28.7</v>
       </c>
       <c r="N11" t="n">
-        <v>980.1</v>
+        <v>27.5</v>
       </c>
       <c r="O11" t="n">
-        <v>19.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>58.5</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>24.2869875222816</v>
       </c>
       <c r="X11" t="n">
-        <v>27.45</v>
+        <v>23.3675988578761</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.26813880126183</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>27.0244461420932</v>
+        <v>1</v>
       </c>
       <c r="AA11" t="n">
-        <v>26.4032150535234</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1841,22 +1755,13 @@
         <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>112</v>
-      </c>
-      <c r="AN11" t="inlineStr"/>
+        <v>106</v>
+      </c>
+      <c r="AK11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>54391258</v>
+        <v>53959319</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1864,74 +1769,80 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>83.09377138945931</v>
-      </c>
-      <c r="D12" t="inlineStr"/>
+        <v>82.8637919233402</v>
+      </c>
+      <c r="D12" t="n">
+        <v>24.7251829329413</v>
+      </c>
       <c r="E12" t="n">
-        <v>23.5078053259871</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>55</v>
+      </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="n">
-        <v>55</v>
-      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>331</v>
+      </c>
+      <c r="M12" t="n">
+        <v>197</v>
+      </c>
+      <c r="N12" t="n">
+        <v>113</v>
+      </c>
       <c r="O12" t="n">
-        <v>131</v>
+        <v>641</v>
       </c>
       <c r="P12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>244</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>405</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>29</v>
+        <v>24.1</v>
       </c>
       <c r="V12" t="n">
-        <v>29</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>25.4011289174665</v>
       </c>
       <c r="X12" t="n">
-        <v>27.2</v>
+        <v>24.50428063210799</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="Z12" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>575</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1940,33 +1851,24 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="AK12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>176</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>132</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>54668287</v>
+        <v>55049412</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1974,74 +1876,80 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>78.1382614647502</v>
-      </c>
-      <c r="D13" t="inlineStr"/>
+        <v>78.2340862422998</v>
+      </c>
+      <c r="D13" t="n">
+        <v>24.6913580246914</v>
+      </c>
       <c r="E13" t="n">
-        <v>22.6940189315895</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>60</v>
+      </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="n">
-        <v>35</v>
-      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>345</v>
+      </c>
+      <c r="M13" t="n">
+        <v>210</v>
+      </c>
+      <c r="N13" t="n">
+        <v>308</v>
+      </c>
       <c r="O13" t="n">
-        <v>114</v>
+        <v>863</v>
       </c>
       <c r="P13" t="n">
-        <v>179</v>
+        <v>14</v>
       </c>
       <c r="Q13" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>469</v>
+        <v>26</v>
       </c>
       <c r="S13" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="T13" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>94</v>
+        <v>24.1</v>
       </c>
       <c r="V13" t="n">
-        <v>163</v>
+        <v>0.28</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>25.46479089470326</v>
       </c>
       <c r="X13" t="n">
-        <v>25.8</v>
+        <v>24.41839631915816</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>85.40000000000001</v>
+        <v>1</v>
       </c>
       <c r="AA13" t="n">
-        <v>546.5</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2053,30 +1961,21 @@
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>242</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>120</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>53613169</v>
+        <v>54908834</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2084,85 +1983,83 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>74.92402464065709</v>
-      </c>
-      <c r="D14" t="inlineStr"/>
+        <v>82.2231348391513</v>
+      </c>
+      <c r="D14" t="n">
+        <v>29.7619047619048</v>
+      </c>
       <c r="E14" t="n">
-        <v>25.0995015956112</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>55</v>
+      </c>
       <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>60</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>304</v>
-      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>457</v>
+        <v>482</v>
       </c>
       <c r="M14" t="n">
-        <v>267</v>
+        <v>500</v>
       </c>
       <c r="N14" t="n">
-        <v>1029</v>
+        <v>726</v>
       </c>
       <c r="O14" t="n">
-        <v>296</v>
+        <v>1708</v>
       </c>
       <c r="P14" t="n">
-        <v>409</v>
+        <v>7</v>
       </c>
       <c r="Q14" t="n">
-        <v>243</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>947</v>
+        <v>130</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>30.1</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="W14" t="n">
-        <v>2</v>
+        <v>31.60817169805041</v>
       </c>
       <c r="X14" t="n">
-        <v>24.7</v>
+        <v>29.00614919566187</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>79.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>471.8</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2171,30 +2068,21 @@
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
         <v>150</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>174</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>54650485</v>
+        <v>54970493</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2202,71 +2090,77 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>83.93702943189599</v>
-      </c>
-      <c r="D15" t="inlineStr"/>
+        <v>77.1033538672142</v>
+      </c>
+      <c r="D15" t="n">
+        <v>34.6666666666667</v>
+      </c>
       <c r="E15" t="n">
-        <v>23.3843537414966</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>55</v>
+      </c>
       <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>45</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>107</v>
+      </c>
+      <c r="M15" t="n">
+        <v>149</v>
+      </c>
+      <c r="N15" t="n">
+        <v>82</v>
+      </c>
       <c r="O15" t="n">
-        <v>80</v>
+        <v>338</v>
       </c>
       <c r="P15" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>21.9</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="W15" t="n">
-        <v>2</v>
+        <v>21.8997201694448</v>
       </c>
       <c r="X15" t="n">
-        <v>21.4</v>
+        <v>21.71360410930048</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="Z15" t="n">
-        <v>72.20999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>373.8</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2275,7 +2169,7 @@
         <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -2284,27 +2178,18 @@
         <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>162</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>53704270</v>
+        <v>51855783</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2312,119 +2197,114 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>82.009582477755</v>
+        <v>75.41957563312801</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>24.4265887509131</v>
       </c>
       <c r="E16" t="n">
-        <v>24.1588179685585</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>43</v>
+      </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>50</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
+        <v>1077</v>
+      </c>
+      <c r="I16" t="n">
+        <v>961</v>
+      </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>1198</v>
       </c>
       <c r="K16" t="n">
-        <v>487</v>
+        <v>3236</v>
       </c>
       <c r="L16" t="n">
-        <v>174</v>
+        <v>1077</v>
       </c>
       <c r="M16" t="n">
-        <v>162</v>
+        <v>864</v>
       </c>
       <c r="N16" t="n">
-        <v>824</v>
+        <v>1198</v>
       </c>
       <c r="O16" t="n">
-        <v>487</v>
+        <v>3139</v>
       </c>
       <c r="P16" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>162</v>
+        <v>70</v>
       </c>
       <c r="R16" t="n">
-        <v>776</v>
+        <v>460</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>530</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>28.4</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="W16" t="n">
-        <v>2</v>
+        <v>30.84422797120932</v>
       </c>
       <c r="X16" t="n">
-        <v>23.5</v>
+        <v>29.53250900522315</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.31</v>
+        <v>1</v>
       </c>
       <c r="Z16" t="n">
-        <v>81.8</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>468.7</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="AK16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>165</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>108</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>51499972</v>
+        <v>53788380</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2432,113 +2312,110 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>79.8384668035592</v>
-      </c>
-      <c r="D17" t="inlineStr"/>
+        <v>89.3661875427789</v>
+      </c>
+      <c r="D17" t="n">
+        <v>28.0816326530612</v>
+      </c>
       <c r="E17" t="n">
-        <v>24.5674740484429</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>59</v>
+      </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>55</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
+        <v>331</v>
+      </c>
+      <c r="I17" t="n">
+        <v>21</v>
+      </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="K17" t="n">
-        <v>300</v>
+        <v>472</v>
       </c>
       <c r="L17" t="n">
-        <v>279</v>
+        <v>331</v>
       </c>
       <c r="M17" t="n">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="N17" t="n">
-        <v>691</v>
+        <v>95</v>
       </c>
       <c r="O17" t="n">
-        <v>260</v>
+        <v>447</v>
       </c>
       <c r="P17" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>456</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>30.8</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W17" t="n">
-        <v>2</v>
+        <v>32.18112949318124</v>
       </c>
       <c r="X17" t="n">
-        <v>23.6</v>
+        <v>30.81735511717315</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.27</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="n">
-        <v>76.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>430.2</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
       </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="inlineStr"/>
-      <c r="AN17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>55106789</v>
+        <v>54292554</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2546,77 +2423,83 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>73.5468856947296</v>
-      </c>
-      <c r="D18" t="inlineStr"/>
+        <v>86.08350444900751</v>
+      </c>
+      <c r="D18" t="n">
+        <v>21.7993079584775</v>
+      </c>
       <c r="E18" t="n">
-        <v>33.9125133363816</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>37</v>
+      </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="n">
-        <v>55</v>
-      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>129</v>
+      </c>
+      <c r="M18" t="n">
+        <v>30</v>
+      </c>
+      <c r="N18" t="n">
+        <v>94</v>
+      </c>
       <c r="O18" t="n">
-        <v>160</v>
+        <v>253</v>
       </c>
       <c r="P18" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>247</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>27.8</v>
       </c>
       <c r="V18" t="n">
-        <v>6</v>
+        <v>0.23</v>
       </c>
       <c r="W18" t="n">
-        <v>2</v>
+        <v>28.45690382483089</v>
       </c>
       <c r="X18" t="n">
-        <v>25.2</v>
+        <v>27.94191276257948</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="Z18" t="n">
-        <v>82.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>501.8</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -2625,30 +2508,21 @@
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>202</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>90</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>52019412</v>
+        <v>52671077</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2656,82 +2530,88 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>75.6714579055441</v>
-      </c>
-      <c r="D19" t="inlineStr"/>
+        <v>82.9924709103354</v>
+      </c>
+      <c r="D19" t="n">
+        <v>20.829995193078</v>
+      </c>
       <c r="E19" t="n">
-        <v>26.5432098765432</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>55</v>
+      </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>60</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
+        <v>507</v>
+      </c>
+      <c r="I19" t="n">
+        <v>748</v>
+      </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>531</v>
       </c>
       <c r="K19" t="n">
-        <v>32</v>
+        <v>1786</v>
       </c>
       <c r="L19" t="n">
-        <v>98</v>
+        <v>506</v>
       </c>
       <c r="M19" t="n">
-        <v>38</v>
+        <v>271</v>
       </c>
       <c r="N19" t="n">
-        <v>167</v>
+        <v>478</v>
       </c>
       <c r="O19" t="n">
-        <v>32</v>
+        <v>1255</v>
       </c>
       <c r="P19" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>26.1</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>26.67436846220166</v>
       </c>
       <c r="X19" t="n">
-        <v>28.1</v>
+        <v>25.90852925166494</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>88.40000000000001</v>
+        <v>1</v>
       </c>
       <c r="AA19" t="n">
-        <v>595</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2740,33 +2620,24 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="AK19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>196</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>178</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>55595677</v>
+        <v>52081005</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2774,77 +2645,91 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>82.32717316906231</v>
-      </c>
-      <c r="D20" t="inlineStr"/>
+        <v>93.3223819301848</v>
+      </c>
+      <c r="D20" t="n">
+        <v>25.9515570934256</v>
+      </c>
       <c r="E20" t="n">
-        <v>23.8884409806205</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>35</v>
+      </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>40</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
+        <v>451</v>
+      </c>
+      <c r="I20" t="n">
+        <v>473</v>
+      </c>
       <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+        <v>114</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1038</v>
+      </c>
+      <c r="L20" t="n">
+        <v>439</v>
+      </c>
+      <c r="M20" t="n">
+        <v>363</v>
+      </c>
+      <c r="N20" t="n">
+        <v>98</v>
+      </c>
       <c r="O20" t="n">
-        <v>227.91464</v>
+        <v>900</v>
       </c>
       <c r="P20" t="n">
-        <v>475.4452</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>137.97755</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>841.33746</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>29.3</v>
       </c>
       <c r="V20" t="n">
-        <v>127</v>
+        <v>0.27</v>
       </c>
       <c r="W20" t="n">
-        <v>1</v>
+        <v>29.66648139232929</v>
       </c>
       <c r="X20" t="n">
-        <v>26.83374</v>
+        <v>28.60168539601018</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>87.78688</v>
+        <v>1</v>
       </c>
       <c r="AA20" t="n">
-        <v>573.9796</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -2858,25 +2743,12 @@
       <c r="AI20" t="n">
         <v>0</v>
       </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>146</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>148</v>
-      </c>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>51981781</v>
+        <v>51517368</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2884,111 +2756,110 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>69.0513347022587</v>
-      </c>
-      <c r="D21" t="inlineStr"/>
+        <v>83.8713210130048</v>
+      </c>
+      <c r="D21" t="n">
+        <v>28.0689181522291</v>
+      </c>
       <c r="E21" t="n">
-        <v>21.9713358572201</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>50</v>
+      </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>993</v>
+      </c>
+      <c r="I21" t="n">
+        <v>889</v>
+      </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>719</v>
       </c>
       <c r="K21" t="n">
-        <v>303</v>
+        <v>2601</v>
       </c>
       <c r="L21" t="n">
-        <v>459</v>
+        <v>983</v>
       </c>
       <c r="M21" t="n">
-        <v>265</v>
+        <v>880</v>
       </c>
       <c r="N21" t="n">
-        <v>1026</v>
+        <v>720</v>
       </c>
       <c r="O21" t="n">
-        <v>269</v>
+        <v>2583</v>
       </c>
       <c r="P21" t="n">
-        <v>171</v>
+        <v>64</v>
       </c>
       <c r="Q21" t="n">
-        <v>265</v>
+        <v>34</v>
       </c>
       <c r="R21" t="n">
-        <v>704</v>
+        <v>13</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>28.7</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="W21" t="n">
-        <v>1</v>
+        <v>28.52056580206764</v>
       </c>
       <c r="X21" t="n">
-        <v>27.6</v>
+        <v>28.13264475671239</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>88.3</v>
+        <v>1</v>
       </c>
       <c r="AA21" t="n">
-        <v>565</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
       </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="inlineStr"/>
-      <c r="AN21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>51991959</v>
+        <v>53146628</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2996,121 +2867,110 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>78.52429842573579</v>
+        <v>85.5359342915811</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>23.1481481481481</v>
       </c>
       <c r="E22" t="n">
-        <v>22.65625</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>40</v>
-      </c>
-      <c r="I22" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="I22" t="n">
+        <v>190</v>
+      </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>224</v>
       </c>
       <c r="K22" t="n">
-        <v>416</v>
+        <v>512</v>
       </c>
       <c r="L22" t="n">
-        <v>329</v>
+        <v>98</v>
       </c>
       <c r="M22" t="n">
-        <v>530</v>
+        <v>190</v>
       </c>
       <c r="N22" t="n">
-        <v>1275</v>
+        <v>224</v>
       </c>
       <c r="O22" t="n">
-        <v>416</v>
+        <v>512</v>
       </c>
       <c r="P22" t="n">
-        <v>302</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>503</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1221</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>63</v>
+        <v>29.3</v>
       </c>
       <c r="V22" t="n">
-        <v>63</v>
+        <v>0.22</v>
       </c>
       <c r="W22" t="n">
-        <v>2</v>
+        <v>29.73014336956605</v>
       </c>
       <c r="X22" t="n">
-        <v>27.2</v>
+        <v>28.98419313378001</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>87.8</v>
+        <v>1</v>
       </c>
       <c r="AA22" t="n">
-        <v>566.5</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
       </c>
-      <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>164</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>122</v>
-      </c>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>54368304</v>
+        <v>54747624</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3118,74 +2978,80 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>76.766598220397</v>
-      </c>
-      <c r="D23" t="inlineStr"/>
+        <v>74.3572895277207</v>
+      </c>
+      <c r="D23" t="n">
+        <v>24.441802087462</v>
+      </c>
       <c r="E23" t="n">
-        <v>27.1808999081726</v>
-      </c>
-      <c r="F23" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>60</v>
+      </c>
       <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>61</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="L23" t="n">
+        <v>825</v>
+      </c>
+      <c r="M23" t="n">
+        <v>295</v>
+      </c>
+      <c r="N23" t="n">
+        <v>336</v>
+      </c>
       <c r="O23" t="n">
-        <v>218</v>
+        <v>1456</v>
       </c>
       <c r="P23" t="n">
-        <v>474</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>984</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>26.2</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W23" t="n">
-        <v>1</v>
+        <v>26.35605857601787</v>
       </c>
       <c r="X23" t="n">
-        <v>24.2</v>
+        <v>25.87656616663467</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>77.40000000000001</v>
+        <v>1</v>
       </c>
       <c r="AA23" t="n">
-        <v>467.5</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3194,33 +3060,24 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AK23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>122</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>54057310</v>
+        <v>52069147</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3228,77 +3085,83 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>76.2464065708419</v>
-      </c>
-      <c r="D24" t="inlineStr"/>
+        <v>65.55783709787821</v>
+      </c>
+      <c r="D24" t="n">
+        <v>33.9506172839506</v>
+      </c>
       <c r="E24" t="n">
-        <v>24.4646016033724</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>33</v>
+      </c>
       <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>55</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="L24" t="n">
+        <v>70.09854</v>
+      </c>
+      <c r="M24" t="n">
+        <v>161.84105</v>
+      </c>
+      <c r="N24" t="n">
+        <v>295.33548</v>
+      </c>
       <c r="O24" t="n">
-        <v>12</v>
+        <v>527.27507</v>
       </c>
       <c r="P24" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>157</v>
+        <v>128</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>29.530556</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="W24" t="n">
-        <v>2</v>
+        <v>30.31297832046516</v>
       </c>
       <c r="X24" t="n">
-        <v>22.6</v>
+        <v>29.51953448561718</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>71.59999999999999</v>
+        <v>1</v>
       </c>
       <c r="AA24" t="n">
-        <v>392.3</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3307,30 +3170,21 @@
         <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>162</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>108</v>
+        <v>165</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>54973367</v>
+        <v>53508246</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3338,74 +3192,88 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>65.43737166324431</v>
-      </c>
-      <c r="D25" t="inlineStr"/>
+        <v>89.3032169746749</v>
+      </c>
+      <c r="D25" t="n">
+        <v>30.859375</v>
+      </c>
       <c r="E25" t="n">
-        <v>28.3553875236295</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>50</v>
+      </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>55</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
+        <v>397</v>
+      </c>
+      <c r="I25" t="n">
+        <v>334</v>
+      </c>
       <c r="J25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+        <v>158</v>
+      </c>
+      <c r="K25" t="n">
+        <v>889</v>
+      </c>
+      <c r="L25" t="n">
+        <v>397</v>
+      </c>
+      <c r="M25" t="n">
+        <v>301</v>
+      </c>
+      <c r="N25" t="n">
+        <v>95</v>
+      </c>
       <c r="O25" t="n">
-        <v>558</v>
+        <v>793</v>
       </c>
       <c r="P25" t="n">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="Q25" t="n">
-        <v>310</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>966</v>
+        <v>37</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>25.2</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="W25" t="n">
-        <v>1</v>
+        <v>25.27380496299298</v>
       </c>
       <c r="X25" t="n">
-        <v>27.5</v>
+        <v>24.87557876193615</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>87.59999999999999</v>
+        <v>1</v>
       </c>
       <c r="AA25" t="n">
-        <v>592.1</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3423,20 +3291,15 @@
         <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="AK25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="inlineStr"/>
-      <c r="AN25" t="inlineStr"/>
+        <v>157</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>52511921</v>
+        <v>51961920</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3444,86 +3307,86 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>84.75290896646131</v>
+        <v>85.864476386037</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>23.5555555555556</v>
       </c>
       <c r="E26" t="n">
-        <v>33.984375</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>55</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
+        <v>456</v>
+      </c>
+      <c r="I26" t="n">
+        <v>379</v>
+      </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>506</v>
       </c>
       <c r="K26" t="n">
-        <v>131</v>
+        <v>1341</v>
       </c>
       <c r="L26" t="n">
-        <v>234</v>
+        <v>392</v>
       </c>
       <c r="M26" t="n">
-        <v>269</v>
+        <v>352</v>
       </c>
       <c r="N26" t="n">
-        <v>635</v>
+        <v>506</v>
       </c>
       <c r="O26" t="n">
-        <v>114</v>
+        <v>1250</v>
       </c>
       <c r="P26" t="n">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="S26" t="n">
-        <v>105</v>
+        <v>571</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
-        <v>310</v>
+        <v>26.8</v>
       </c>
       <c r="V26" t="n">
-        <v>415</v>
+        <v>0.29</v>
       </c>
       <c r="W26" t="n">
-        <v>2</v>
+        <v>27.05634032562221</v>
       </c>
       <c r="X26" t="n">
-        <v>26</v>
+        <v>26.08484641907004</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>83.90000000000001</v>
+        <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>526.6</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3532,29 +3395,20 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
       </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="inlineStr"/>
-      <c r="AN26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>53256397</v>
+        <v>52595914</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3562,84 +3416,88 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>82.694045174538</v>
+        <v>79.9315537303217</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>23.4375</v>
       </c>
       <c r="E27" t="n">
-        <v>35.0127796645776</v>
-      </c>
-      <c r="F27" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>40</v>
+      </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>55</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
+        <v>140</v>
+      </c>
+      <c r="I27" t="n">
+        <v>180</v>
+      </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="K27" t="n">
-        <v>184</v>
+        <v>419</v>
       </c>
       <c r="L27" t="n">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="M27" t="n">
-        <v>209</v>
+        <v>87</v>
       </c>
       <c r="N27" t="n">
-        <v>535</v>
+        <v>93</v>
       </c>
       <c r="O27" t="n">
-        <v>184</v>
+        <v>320</v>
       </c>
       <c r="P27" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>531</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>15</v>
+        <v>23.1</v>
       </c>
       <c r="V27" t="n">
-        <v>127</v>
+        <v>0.29</v>
       </c>
       <c r="W27" t="n">
-        <v>1</v>
+        <v>22.95014279385131</v>
       </c>
       <c r="X27" t="n">
-        <v>25.9</v>
+        <v>22.02219204778724</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>84.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>511.5</v>
+        <v>1</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3651,30 +3509,17 @@
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>199</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>324</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>51322415</v>
+        <v>54897342</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3682,89 +3527,83 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>86.072553045859</v>
+        <v>83.8384668035592</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>29.4117647058824</v>
       </c>
       <c r="E28" t="n">
-        <v>20.1234567901235</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
       </c>
-      <c r="H28" t="n">
-        <v>70</v>
-      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>600</v>
-      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
-        <v>419</v>
+        <v>574</v>
       </c>
       <c r="M28" t="n">
-        <v>611</v>
+        <v>719</v>
       </c>
       <c r="N28" t="n">
-        <v>1631</v>
+        <v>1014</v>
       </c>
       <c r="O28" t="n">
-        <v>600</v>
+        <v>2307</v>
       </c>
       <c r="P28" t="n">
-        <v>359</v>
+        <v>22</v>
       </c>
       <c r="Q28" t="n">
-        <v>604</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1564</v>
+        <v>400</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>422</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W28" t="n">
-        <v>1</v>
+        <v>29.85746732403956</v>
       </c>
       <c r="X28" t="n">
-        <v>27.1</v>
+        <v>24.010890567742</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>86.2</v>
+        <v>1</v>
       </c>
       <c r="AA28" t="n">
-        <v>547.9</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -3776,27 +3615,18 @@
         <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1</v>
+        <v>124</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>145</v>
+        <v>118</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>51519926</v>
+        <v>55734071</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3804,77 +3634,71 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>80.1232032854209</v>
+        <v>85.23477070499661</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>17.9282154254366</v>
       </c>
       <c r="E29" t="n">
-        <v>35.3212373587151</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>40</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>472</v>
-      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
-        <v>963</v>
+        <v>429.47736</v>
       </c>
       <c r="M29" t="n">
-        <v>505</v>
+        <v>115.17869</v>
       </c>
       <c r="N29" t="n">
-        <v>1940</v>
+        <v>88.60468</v>
       </c>
       <c r="O29" t="n">
-        <v>493</v>
+        <v>633.26073</v>
       </c>
       <c r="P29" t="n">
-        <v>839</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>486</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1819</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>5</v>
+        <v>23.781143</v>
       </c>
       <c r="V29" t="n">
-        <v>148</v>
+        <v>0.2</v>
       </c>
       <c r="W29" t="n">
-        <v>1</v>
+        <v>23.77834692051519</v>
       </c>
       <c r="X29" t="n">
-        <v>28.6</v>
+        <v>23.51834656646476</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="Z29" t="n">
-        <v>90.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>650.6</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -3901,24 +3725,15 @@
         <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="AK29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>216</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>118</v>
+        <v>170</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>51763278</v>
+        <v>53993439</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3926,79 +3741,77 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>76.46269678302529</v>
-      </c>
-      <c r="D30" t="inlineStr"/>
+        <v>88.6570841889117</v>
+      </c>
+      <c r="D30" t="n">
+        <v>25.2493372048984</v>
+      </c>
       <c r="E30" t="n">
-        <v>31.5558802045289</v>
-      </c>
-      <c r="F30" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>31</v>
+      </c>
       <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>30</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>282</v>
-      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
-        <v>563</v>
+        <v>73</v>
       </c>
       <c r="M30" t="n">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="N30" t="n">
-        <v>948</v>
+        <v>60</v>
       </c>
       <c r="O30" t="n">
-        <v>272</v>
+        <v>213</v>
       </c>
       <c r="P30" t="n">
-        <v>309</v>
+        <v>28</v>
       </c>
       <c r="Q30" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>667</v>
+        <v>21</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>24.1</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>24.15972036134972</v>
       </c>
       <c r="X30" t="n">
-        <v>30</v>
+        <v>23.43662816189115</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>93.90000000000001</v>
+        <v>1</v>
       </c>
       <c r="AA30" t="n">
-        <v>676.5</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4007,32 +3820,27 @@
         <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="AK30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="inlineStr"/>
-      <c r="AN30" t="inlineStr"/>
+        <v>106</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>52595914</v>
+        <v>53798246</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -4040,77 +3848,71 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>79.9315537303217</v>
+        <v>74.0177960301164</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>33.3049886621315</v>
       </c>
       <c r="E31" t="n">
-        <v>23.4375</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
       </c>
-      <c r="H31" t="n">
-        <v>40</v>
-      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" t="n">
-        <v>140</v>
-      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="M31" t="n">
-        <v>99</v>
+        <v>201</v>
       </c>
       <c r="N31" t="n">
-        <v>419</v>
+        <v>284</v>
       </c>
       <c r="O31" t="n">
-        <v>140</v>
+        <v>678</v>
       </c>
       <c r="P31" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>93</v>
+        <v>5</v>
       </c>
       <c r="R31" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="W31" t="n">
-        <v>2</v>
+        <v>28.26591789312061</v>
       </c>
       <c r="X31" t="n">
-        <v>23.1</v>
+        <v>27.36639362819337</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.29</v>
+        <v>1</v>
       </c>
       <c r="Z31" t="n">
-        <v>72.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>380.9</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
@@ -4125,32 +3927,27 @@
         <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="AK31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="inlineStr"/>
-      <c r="AN31" t="inlineStr"/>
+        <v>130</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>53392099</v>
+        <v>55064132</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4158,84 +3955,80 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>78.9869952087611</v>
+        <v>80.7802874743327</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>28.7267877295578</v>
       </c>
       <c r="E32" t="n">
-        <v>25.469387755102</v>
-      </c>
-      <c r="F32" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>53</v>
+      </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
-      <c r="H32" t="n">
-        <v>48</v>
-      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" t="n">
-        <v>770</v>
-      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="n">
-        <v>530</v>
+        <v>209</v>
       </c>
       <c r="M32" t="n">
-        <v>406</v>
+        <v>146</v>
       </c>
       <c r="N32" t="n">
-        <v>1705</v>
+        <v>146</v>
       </c>
       <c r="O32" t="n">
-        <v>700</v>
+        <v>501</v>
       </c>
       <c r="P32" t="n">
-        <v>490</v>
+        <v>38</v>
       </c>
       <c r="Q32" t="n">
-        <v>370</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1559</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>144</v>
+        <v>38</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>72</v>
+        <v>25.6</v>
       </c>
       <c r="V32" t="n">
-        <v>216</v>
+        <v>0.25</v>
       </c>
       <c r="W32" t="n">
-        <v>1</v>
+        <v>25.68760781503191</v>
       </c>
       <c r="X32" t="n">
-        <v>31.4</v>
+        <v>25.12259624969562</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>101.3</v>
+        <v>1</v>
       </c>
       <c r="AA32" t="n">
-        <v>780.1</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4253,24 +4046,15 @@
         <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="AK32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>164</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>111</v>
+        <v>149</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>51903886</v>
+        <v>52046931</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -4278,83 +4062,83 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>81.96303901437371</v>
+        <v>89.0458590006845</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>19.3961882273571</v>
       </c>
       <c r="E33" t="n">
-        <v>24.8015873015873</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>70</v>
-      </c>
-      <c r="I33" t="inlineStr"/>
+        <v>116</v>
+      </c>
+      <c r="I33" t="n">
+        <v>191</v>
+      </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="K33" t="n">
-        <v>216</v>
+        <v>393</v>
       </c>
       <c r="L33" t="n">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="M33" t="n">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="N33" t="n">
-        <v>403</v>
+        <v>86</v>
       </c>
       <c r="O33" t="n">
-        <v>216</v>
+        <v>323</v>
       </c>
       <c r="P33" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>349</v>
+        <v>38</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>26.8</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="W33" t="n">
-        <v>2</v>
+        <v>27.05634032562221</v>
       </c>
       <c r="X33" t="n">
-        <v>27.2</v>
+        <v>26.40744778753616</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>88.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>567.3</v>
+        <v>1</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -4363,7 +4147,7 @@
         <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -4372,23 +4156,18 @@
         <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM33" t="inlineStr"/>
-      <c r="AN33" t="inlineStr"/>
+        <v>164</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>51187778</v>
+        <v>55003420</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -4396,82 +4175,80 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>87.1786447638604</v>
-      </c>
-      <c r="D34" t="inlineStr"/>
+        <v>85.0595482546201</v>
+      </c>
+      <c r="D34" t="n">
+        <v>24.1632653061225</v>
+      </c>
       <c r="E34" t="n">
-        <v>25.9043101026809</v>
-      </c>
-      <c r="F34" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>40</v>
+      </c>
       <c r="G34" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" t="n">
-        <v>60</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" t="n">
-        <v>220</v>
-      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="n">
-        <v>221</v>
+        <v>274</v>
       </c>
       <c r="M34" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="N34" t="n">
-        <v>607</v>
+        <v>127</v>
       </c>
       <c r="O34" t="n">
-        <v>220</v>
+        <v>562</v>
       </c>
       <c r="P34" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>482</v>
+        <v>6</v>
       </c>
       <c r="S34" t="n">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>43</v>
+        <v>25.3</v>
       </c>
       <c r="V34" t="n">
-        <v>82</v>
+        <v>0.21</v>
       </c>
       <c r="W34" t="n">
-        <v>1</v>
+        <v>25.84676275812381</v>
       </c>
       <c r="X34" t="n">
-        <v>24.4</v>
+        <v>25.45739437315213</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>78.90000000000001</v>
+        <v>1</v>
       </c>
       <c r="AA34" t="n">
-        <v>472.4</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -4480,33 +4257,24 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="AK34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>156</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>54396818</v>
+        <v>54291618</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -4514,74 +4282,80 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>87.25804243668721</v>
-      </c>
-      <c r="D35" t="inlineStr"/>
+        <v>79.0198494182067</v>
+      </c>
+      <c r="D35" t="n">
+        <v>25.1428571428571</v>
+      </c>
       <c r="E35" t="n">
-        <v>30.457655947154</v>
-      </c>
-      <c r="F35" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>55</v>
+      </c>
       <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
-        <v>55</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>395</v>
+      </c>
+      <c r="M35" t="n">
+        <v>473</v>
+      </c>
+      <c r="N35" t="n">
+        <v>343</v>
+      </c>
       <c r="O35" t="n">
-        <v>224</v>
+        <v>1211</v>
       </c>
       <c r="P35" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>309</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>25.1</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="W35" t="n">
-        <v>2</v>
+        <v>26.29239659878111</v>
       </c>
       <c r="X35" t="n">
-        <v>24.1</v>
+        <v>25.02611699915164</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>76.09999999999999</v>
+        <v>1</v>
       </c>
       <c r="AA35" t="n">
-        <v>449.5</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -4590,29 +4364,24 @@
         <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AK35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM35" t="inlineStr"/>
-      <c r="AN35" t="inlineStr"/>
+        <v>214</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>51890467</v>
+        <v>53400331</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -4620,80 +4389,80 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>87.57837097878171</v>
-      </c>
-      <c r="D36" t="inlineStr"/>
+        <v>81.9822039698836</v>
+      </c>
+      <c r="D36" t="n">
+        <v>25.5649539199596</v>
+      </c>
       <c r="E36" t="n">
-        <v>32.0105109140315</v>
-      </c>
-      <c r="F36" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>30</v>
+      </c>
       <c r="G36" t="n">
         <v>1</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" t="n">
-        <v>566</v>
-      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
-        <v>830</v>
+        <v>231.88986</v>
       </c>
       <c r="M36" t="n">
-        <v>532</v>
+        <v>216.33243</v>
       </c>
       <c r="N36" t="n">
-        <v>1929</v>
+        <v>132.02795</v>
       </c>
       <c r="O36" t="n">
-        <v>566</v>
+        <v>580.25024</v>
       </c>
       <c r="P36" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>519</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1435</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>25.076103</v>
       </c>
       <c r="V36" t="n">
-        <v>68</v>
+        <v>0.25</v>
       </c>
       <c r="W36" t="n">
-        <v>1</v>
+        <v>24.65239722008612</v>
       </c>
       <c r="X36" t="n">
-        <v>31</v>
+        <v>23.93718682521605</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>96.3</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>718.3</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
@@ -4711,24 +4480,15 @@
         <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AK36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>200</v>
+        <v>129</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>53286546</v>
+        <v>54859265</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -4736,85 +4496,83 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>87.1622176591376</v>
-      </c>
-      <c r="D37" t="inlineStr"/>
+        <v>70.1054072553046</v>
+      </c>
+      <c r="D37" t="n">
+        <v>29.9616116850286</v>
+      </c>
       <c r="E37" t="n">
-        <v>27.1020408163265</v>
-      </c>
-      <c r="F37" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>55</v>
+      </c>
       <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>55</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="n">
-        <v>1</v>
-      </c>
-      <c r="K37" t="n">
-        <v>110</v>
-      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
-        <v>169</v>
+        <v>626</v>
       </c>
       <c r="M37" t="n">
-        <v>142</v>
+        <v>315</v>
       </c>
       <c r="N37" t="n">
-        <v>420</v>
+        <v>291</v>
       </c>
       <c r="O37" t="n">
-        <v>110</v>
+        <v>1232</v>
       </c>
       <c r="P37" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>142</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>373</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>228</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>197</v>
+        <v>26.5</v>
       </c>
       <c r="V37" t="n">
-        <v>425</v>
+        <v>0.25</v>
       </c>
       <c r="W37" t="n">
-        <v>1</v>
+        <v>27.47014317766114</v>
       </c>
       <c r="X37" t="n">
-        <v>25.9</v>
+        <v>26.53730943771464</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>83.7</v>
+        <v>1</v>
       </c>
       <c r="AA37" t="n">
-        <v>489.4</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -4823,22 +4581,17 @@
         <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM37" t="inlineStr"/>
-      <c r="AN37" t="inlineStr"/>
+        <v>112</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
